--- a/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
+++ b/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A6DD490-EDC7-45DC-A82D-CEB04A0F0E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6B9804F-4C05-4094-9ACC-E5EBDF30F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{7052020F-5EE3-45D2-A5BA-A5D539467B0E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{6F8576E5-639A-42B8-A8AF-3A87B1FD4AFB}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="233">
   <si>
     <r>
       <t>ICT</t>
@@ -92,7 +92,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>5</t>
+      <t>10</t>
     </r>
     <r>
       <rPr>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>14</t>
+      <t>8</t>
     </r>
     <r>
       <rPr>
@@ -431,7 +431,42 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>対応している</t>
+      <t>評価不要</t>
+    </r>
+    <rPh sb="0" eb="4">
+      <t>ヒョウカフヨウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>米国リハビリテーション法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>508</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>条を用いているため評価の対象外である。</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -510,6 +545,19 @@
         <charset val="128"/>
       </rPr>
       <t>発話能力なしでの使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対応している</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -2517,7 +2565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A21923-59C2-41B2-B3DE-D46D6244A9F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8E356-6BA4-41A4-B3BD-105FC46A1668}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2819,7 +2867,7 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
         <v>25</v>
       </c>
@@ -2828,30 +2876,30 @@
       <c r="D22" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="38"/>
+      <c r="E22" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
       <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="33"/>
       <c r="C24" s="34"/>
@@ -2868,7 +2916,7 @@
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="40"/>
       <c r="C25" s="41"/>
@@ -2881,7 +2929,7 @@
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="34"/>
@@ -2898,7 +2946,7 @@
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
@@ -2911,12 +2959,12 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="46" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>21</v>
@@ -2928,7 +2976,7 @@
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
@@ -2941,7 +2989,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
@@ -2958,7 +3006,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -2971,7 +3019,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -2984,7 +3032,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -2997,15 +3045,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -3014,7 +3062,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -3055,15 +3103,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -3072,7 +3120,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -3096,7 +3144,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3126,15 +3174,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -3143,7 +3191,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -3167,10 +3215,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -3193,7 +3241,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -3333,7 +3381,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{A6F0BD74-A1E8-4609-A4E7-01153C683A57}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{9BEFCD79-C5FF-4B5B-97E5-C56309A38AB8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3341,7 +3389,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0771092-D5D0-42D9-83FE-300369BB9B5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C8FFFD-5DDA-44E0-9BC6-A0ED01439006}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3354,43 +3402,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3398,36 +3446,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3435,10 +3483,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3456,14 +3504,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3479,15 +3527,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3502,15 +3550,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3525,17 +3573,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3548,10 +3596,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3559,7 +3607,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3571,10 +3619,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3583,7 +3631,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3594,10 +3642,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3607,10 +3655,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3619,10 +3667,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3632,10 +3680,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3644,10 +3692,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3665,17 +3713,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3690,10 +3738,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3711,10 +3759,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3729,17 +3777,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3752,17 +3800,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3775,20 +3823,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3800,20 +3848,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3825,17 +3873,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3851,10 +3899,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3862,7 +3910,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3871,23 +3919,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3896,23 +3944,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -3924,15 +3972,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -3947,15 +3995,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -3970,27 +4018,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -3999,10 +4047,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4020,29 +4068,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4051,10 +4099,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4072,17 +4120,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4097,10 +4145,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4118,30 +4166,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4149,10 +4197,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4170,31 +4218,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4203,10 +4251,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4224,15 +4272,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4247,14 +4295,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4270,10 +4318,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4283,10 +4331,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4295,27 +4343,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4324,10 +4372,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4337,10 +4385,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4349,14 +4397,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4372,10 +4420,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4385,10 +4433,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4397,10 +4445,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4410,10 +4458,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4422,10 +4470,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4443,10 +4491,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4464,10 +4512,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4485,14 +4533,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4508,10 +4556,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4529,15 +4577,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4552,10 +4600,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4573,20 +4621,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4598,10 +4646,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4619,29 +4667,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4650,10 +4698,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4671,10 +4719,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4682,7 +4730,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4694,10 +4742,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4705,7 +4753,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4717,10 +4765,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4728,7 +4776,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4740,10 +4788,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4761,24 +4809,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4790,17 +4838,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4813,20 +4861,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4838,10 +4886,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4859,14 +4907,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4882,10 +4930,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -4903,22 +4951,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -4930,10 +4978,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -4951,31 +4999,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -4984,10 +5032,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5005,29 +5053,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5036,14 +5084,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5051,10 +5099,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5063,43 +5111,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5109,22 +5157,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5134,22 +5182,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5159,32 +5207,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5193,23 +5241,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5218,26 +5266,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5245,23 +5293,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5273,31 +5321,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5306,10 +5354,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5327,15 +5375,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5350,14 +5398,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5365,10 +5413,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5377,22 +5425,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5404,24 +5452,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5433,10 +5481,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5454,24 +5502,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5480,25 +5528,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5507,20 +5555,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5535,24 +5583,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5564,24 +5612,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>

--- a/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
+++ b/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6B9804F-4C05-4094-9ACC-E5EBDF30F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42086467-D9D2-4214-BEFA-EDB09DC082C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{6F8576E5-639A-42B8-A8AF-3A87B1FD4AFB}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="11960" windowHeight="13930" xr2:uid="{AE86ACFA-E6AE-4E3E-87CE-D111D53930E3}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -92,7 +92,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>10</t>
+      <t>5</t>
     </r>
     <r>
       <rPr>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>8</t>
+      <t>14</t>
     </r>
     <r>
       <rPr>
@@ -2565,7 +2565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8E356-6BA4-41A4-B3BD-105FC46A1668}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE3C425-96BD-4457-AEDB-E16C5468AB58}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3381,7 +3381,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{9BEFCD79-C5FF-4B5B-97E5-C56309A38AB8}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{9AB1C53A-605F-4F23-8EEE-23471F98AEE1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3389,7 +3389,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C8FFFD-5DDA-44E0-9BC6-A0ED01439006}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527D5664-EEC3-46BA-81E8-802426236DBD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
+++ b/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42086467-D9D2-4214-BEFA-EDB09DC082C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5BDBECB-2067-4654-9D2D-BED015E97DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="11960" windowHeight="13930" xr2:uid="{AE86ACFA-E6AE-4E3E-87CE-D111D53930E3}"/>
+    <workbookView xWindow="2280" yWindow="1110" windowWidth="11960" windowHeight="13930" xr2:uid="{821F4FEC-E08A-4511-98C9-963906977E8F}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="235">
   <si>
     <r>
       <t>ICT</t>
@@ -92,7 +92,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>5</t>
+      <t>10</t>
     </r>
     <r>
       <rPr>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>14</t>
+      <t>8</t>
     </r>
     <r>
       <rPr>
@@ -559,6 +559,9 @@
       </rPr>
       <t>対応している</t>
     </r>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -570,72 +573,98 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>すべての製品において要件を満たす。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた器用さ又は力での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた手の届く範囲での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>光の点滅による影響の最小化（光感受性発作）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対応している</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -2565,7 +2594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE3C425-96BD-4457-AEDB-E16C5468AB58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6309012-AA42-48D3-8343-86898D4445DA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2867,7 +2896,7 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
     </row>
-    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
         <v>25</v>
       </c>
@@ -2966,30 +2995,30 @@
       <c r="D28" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="38"/>
+      <c r="E28" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
       <c r="D29" s="47"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
@@ -3006,7 +3035,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -3019,7 +3048,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -3032,7 +3061,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -3045,15 +3074,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -3062,7 +3091,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -3103,15 +3132,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -3120,7 +3149,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -3144,7 +3173,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3174,15 +3203,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -3191,7 +3220,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -3215,10 +3244,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -3241,7 +3270,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -3381,7 +3410,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{9AB1C53A-605F-4F23-8EEE-23471F98AEE1}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{7FDD0E58-2B0A-41D6-B796-A94D1FB4EE4D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3389,7 +3418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527D5664-EEC3-46BA-81E8-802426236DBD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{735BD339-478F-435A-BDFB-2DA605D68E02}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3402,43 +3431,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3446,36 +3475,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3483,10 +3512,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3504,14 +3533,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3527,15 +3556,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3550,15 +3579,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3573,17 +3602,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3596,10 +3625,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3607,7 +3636,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3619,10 +3648,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3631,7 +3660,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3642,10 +3671,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3655,10 +3684,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3667,10 +3696,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3680,10 +3709,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3692,10 +3721,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3713,17 +3742,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3738,10 +3767,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3759,10 +3788,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3777,17 +3806,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3800,17 +3829,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3823,20 +3852,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3848,20 +3877,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3873,17 +3902,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3899,10 +3928,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3910,7 +3939,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3919,23 +3948,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3944,23 +3973,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -3972,15 +4001,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -3995,15 +4024,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4018,27 +4047,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4047,10 +4076,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4068,29 +4097,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4099,10 +4128,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4120,17 +4149,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4145,10 +4174,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4166,30 +4195,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4197,10 +4226,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4218,31 +4247,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4251,10 +4280,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4272,15 +4301,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4295,14 +4324,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4318,10 +4347,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4331,10 +4360,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4343,27 +4372,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4372,10 +4401,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4385,10 +4414,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4397,14 +4426,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4420,10 +4449,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4433,10 +4462,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4445,10 +4474,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4458,10 +4487,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4470,10 +4499,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4491,10 +4520,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4512,10 +4541,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4533,14 +4562,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4556,10 +4585,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4577,15 +4606,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4600,10 +4629,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4621,20 +4650,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4646,10 +4675,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4667,29 +4696,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4698,10 +4727,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4719,10 +4748,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4730,7 +4759,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4742,10 +4771,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4753,7 +4782,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4765,10 +4794,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4776,7 +4805,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4788,10 +4817,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4809,24 +4838,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4838,17 +4867,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4861,20 +4890,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4886,10 +4915,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4907,14 +4936,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4930,10 +4959,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -4951,22 +4980,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -4978,10 +5007,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -4999,31 +5028,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5032,10 +5061,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5053,29 +5082,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5084,14 +5113,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5099,10 +5128,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5111,43 +5140,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5157,22 +5186,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5182,22 +5211,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5207,32 +5236,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5241,23 +5270,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5266,26 +5295,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5293,23 +5322,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5321,31 +5350,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5354,10 +5383,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5375,15 +5404,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5398,14 +5427,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5413,10 +5442,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5425,22 +5454,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5452,24 +5481,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5481,10 +5510,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5502,24 +5531,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5528,25 +5557,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5555,20 +5584,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5583,24 +5612,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5612,24 +5641,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>

--- a/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
+++ b/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5BDBECB-2067-4654-9D2D-BED015E97DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E398885-AF74-43C9-87AE-5AE85133B4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="1110" windowWidth="11960" windowHeight="13930" xr2:uid="{821F4FEC-E08A-4511-98C9-963906977E8F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{77F08E72-DC1A-4710-9794-530970617F9E}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -2594,7 +2594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6309012-AA42-48D3-8343-86898D4445DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF784253-DADB-4DA8-BB8E-69B5C4E32DFF}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3410,7 +3410,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{7FDD0E58-2B0A-41D6-B796-A94D1FB4EE4D}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{772EA2BF-CC06-42BC-B2CC-5091DE2FA2D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3418,7 +3418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{735BD339-478F-435A-BDFB-2DA605D68E02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B99CBF-A2D8-4FE1-AA21-2010A06892E4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
+++ b/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E398885-AF74-43C9-87AE-5AE85133B4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BEB3E55-43E5-4D98-870A-02CE2D0B38E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{77F08E72-DC1A-4710-9794-530970617F9E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{5110C295-B1A8-456D-9260-E44D168763D1}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -92,7 +92,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>10</t>
+      <t>5</t>
     </r>
     <r>
       <rPr>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>8</t>
+      <t>14</t>
     </r>
     <r>
       <rPr>
@@ -2594,7 +2594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF784253-DADB-4DA8-BB8E-69B5C4E32DFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6CE0765-D14A-49E1-86B2-BB7732B2EBDC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3410,7 +3410,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{772EA2BF-CC06-42BC-B2CC-5091DE2FA2D1}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{9400BA4F-3D5A-453A-86A4-5CCD6D2F9F08}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3418,7 +3418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B99CBF-A2D8-4FE1-AA21-2010A06892E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9091418-BDB9-4887-B02D-32864A2D5B2F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
+++ b/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BEB3E55-43E5-4D98-870A-02CE2D0B38E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F862ED1A-FAC1-4B26-B308-61B177B9D4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{5110C295-B1A8-456D-9260-E44D168763D1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{76CCE522-61D9-4FAF-8D6E-3C84CC487E7E}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -92,7 +92,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>5</t>
+      <t>10</t>
     </r>
     <r>
       <rPr>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>14</t>
+      <t>8</t>
     </r>
     <r>
       <rPr>
@@ -192,7 +192,6 @@
   </si>
   <si>
     <t>Insights(Win32,Web,Android,iOS)</t>
-    <phoneticPr fontId="4"/>
   </si>
   <si>
     <r>
@@ -1683,7 +1682,7 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="36"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2594,8 +2593,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6CE0765-D14A-49E1-86B2-BB7732B2EBDC}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0A005FD-B30B-468F-A6FD-5A82171C81A4}">
+  <sheetPr codeName="Sheet239">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -3410,7 +3409,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{9400BA4F-3D5A-453A-86A4-5CCD6D2F9F08}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{50851CAB-D623-4AD8-84C4-10A5D8B13351}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3418,7 +3417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9091418-BDB9-4887-B02D-32864A2D5B2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA186AD-8532-4771-9D5D-8DE56EC95000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
+++ b/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F862ED1A-FAC1-4B26-B308-61B177B9D4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E697085D-D786-4DDF-8914-7D6ADFCD3354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{76CCE522-61D9-4FAF-8D6E-3C84CC487E7E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{3E47D973-0004-4748-B330-617A673FFFBE}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,802 +38,200 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="235">
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービスのアクセシビリティ自己評価様式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>作成日：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品画像</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>企業・団体名</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日本マイクロソフト株式会社</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="226">
+  <si>
+    <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
+  </si>
+  <si>
+    <t>作成日：2024年5月14日</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品画像</t>
+  </si>
+  <si>
+    <t>企業・団体名</t>
+  </si>
+  <si>
+    <t>日本マイクロソフト株式会社</t>
     <rPh sb="0" eb="2">
       <t>ニホン</t>
     </rPh>
     <rPh sb="9" eb="13">
       <t>カブシキガイシャ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Insights
 (Win32,Web,Android,iOS)</t>
   </si>
   <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス名称</t>
-    </r>
+    <t>ICT機器・サービス名称</t>
   </si>
   <si>
     <t>Insights(Win32,Web,Android,iOS)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>型番</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Insights(Win32,Web,Android,iOS)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>は、教育者向けに学習成果の向上を支援するスマート分析機能を提供します。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>問合せ先</t>
-    </r>
+    <t>型番</t>
+  </si>
+  <si>
+    <t>ICT機器・サービス概要</t>
+  </si>
+  <si>
+    <t>Insights(Win32,Web,Android,iOS)は、教育者向けに学習成果の向上を支援するスマート分析機能を提供します。</t>
+  </si>
+  <si>
+    <t>問合せ先</t>
   </si>
   <si>
     <t>0120-167-400</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ウェブサイト</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>URL</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ウェブサイトURL</t>
   </si>
   <si>
     <t>https://www.microsoft.com/ja-jp/microsoft-365/microsoft-teams/education</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機能性能</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配慮対象アクセス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価結果</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>視力なしでの使用（全盲）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた視力での使用（弱視、ロービジョン）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>色知覚なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価不要</t>
-    </r>
+    <t>機能性能</t>
+  </si>
+  <si>
+    <t>配慮対象アクセス</t>
+  </si>
+  <si>
+    <t>評価結果</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>視力なしでの使用（全盲）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた視力での使用（弱視、ロービジョン）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>色知覚なしでの使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>評価不要</t>
     <rPh sb="0" eb="4">
       <t>ヒョウカフヨウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条を用いているため評価の対象外である。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>聴力なしでの使用（全ろう）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた聴力での使用（難聴）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>発話能力なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条を用いているため評価の対象外である。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>聴力なしでの使用（全ろう）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた聴力での使用（難聴）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+  </si>
+  <si>
+    <t>発話能力なしでの使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
     <rPh sb="0" eb="2">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>光の点滅による影響の最小化（光感受性発作）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた器用さ又は力での使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた手の届く範囲での使用</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>光の点滅による影響の最小化（光感受性発作）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>対応している</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
     <rPh sb="4" eb="6">
       <t>セイヒン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>プライバシー</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>サポート対応　概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ドキュメントとサポートサービス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>FAX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>等）が提供されているか。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>用いた技術基準</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>免責事項</t>
-    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
+  </si>
+  <si>
+    <t>プライバシー</t>
+  </si>
+  <si>
+    <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>サポート対応　概要</t>
+  </si>
+  <si>
+    <t>ドキュメントとサポートサービス</t>
+  </si>
+  <si>
+    <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、FAX等）が提供されているか。</t>
+  </si>
+  <si>
+    <t>用いた技術基準</t>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>免責事項</t>
   </si>
   <si>
     <t>章・項・節</t>
@@ -846,18 +244,18 @@
     <rPh sb="4" eb="5">
       <t>セツ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provision Title</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
       <t>コウモクメイ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>規格内容</t>
@@ -867,84 +265,48 @@
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>視力なしでの使用（全盲）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた視力での使用（弱視、ロービジョン）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>色知覚なしでの使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>聴力なしでの使用（全ろう）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた聴力での使用（難聴）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>発話能力なしでの使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた器用さ又は力での使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>限られた手の届く範囲での使用</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>光の点滅による影響の最小化（光感受性発作）</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>General</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
     <rPh sb="0" eb="2">
       <t>イッパン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Functional Performance Criteria</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>機能的性能基準</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Vision</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視力なし</t>
     <rPh sb="0" eb="2">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
   </si>
   <si>
     <t>With Limited Vision</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた視力</t>
@@ -954,11 +316,11 @@
     <rPh sb="4" eb="6">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Perception of Color</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>色彩感覚なし</t>
@@ -968,22 +330,22 @@
     <rPh sb="2" eb="4">
       <t>カンカク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Without Hearing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>聴力なし</t>
     <rPh sb="0" eb="2">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>With Limited Hearing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた聴力</t>
@@ -993,22 +355,22 @@
     <rPh sb="4" eb="6">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Speech</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>発話能力なし</t>
     <rPh sb="0" eb="4">
       <t>ハツワノウリョク</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Manipulation</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限定的な操作</t>
@@ -1018,11 +380,11 @@
     <rPh sb="4" eb="6">
       <t>ソウサ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Reach and Strength</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた手の届く範囲と力の強さ</t>
@@ -1032,138 +394,138 @@
     <rPh sb="13" eb="14">
       <t>ツヨ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Language, Cognitive, and Learning Abilities</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた言語能力、認知能力、学習能力</t>
     <rPh sb="0" eb="1">
       <t>カギ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Closed Functionality</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>クローズドな機能</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech-Output Enabled</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力可能</t>
   </si>
   <si>
     <t>402.2.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Information Displayed On-Screen</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 画面に表示される情報</t>
   </si>
   <si>
     <t>402.2.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Transactional Outputs</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>トランザクション出力</t>
   </si>
   <si>
     <t>402.2.3</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech Delivery Type and Coordination</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声配信の種類と連携</t>
   </si>
   <si>
     <t>402.2.4</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>User Control</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ユーザーコントロール</t>
   </si>
   <si>
     <t>402.2.5</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Braille Instructions</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 点字説明</t>
   </si>
   <si>
     <t>Volume</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音量</t>
   </si>
   <si>
     <t>402.3.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Private Listening</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人的な聞き取り</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>402.3.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Non-Private Listening</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>非個人的な聞き取り</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve">Characters on Display Screens
 </t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ディスプレイ上の文字</t>
   </si>
   <si>
     <t>Characters on Variable Message Signs</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可変メッセージ看板の文字</t>
   </si>
   <si>
     <t>Biometrics</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>バイオメトリクス</t>
@@ -1176,88 +538,88 @@
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティのための情報の保存</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Privacy</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人情報保護</t>
   </si>
   <si>
     <t>Standard Connections</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>標準接続</t>
   </si>
   <si>
     <t>Operable Parts</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作可能な部品</t>
   </si>
   <si>
     <t xml:space="preserve"> Contrast</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コントラスト</t>
   </si>
   <si>
     <t xml:space="preserve"> Input Controls (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 入力コントロール（およびその下位規定）</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Key Repeat</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キーリピート</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Timed Response</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>時限反応</t>
   </si>
   <si>
     <t>Operation</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作方法</t>
   </si>
   <si>
     <t xml:space="preserve"> Keys, Tickets, and Fare Cards</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> キー、チケット、料金カード</t>
     <rPh sb="9" eb="11">
       <t>リョウキン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Reach Height (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>届く高さ（およびその下位規定）</t>
@@ -1267,32 +629,32 @@
     <rPh sb="2" eb="3">
       <t>タカ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display Screens</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>表示画面</t>
   </si>
   <si>
     <t>Visibility</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視認性</t>
   </si>
   <si>
     <t>Flashing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>点滅表示</t>
   </si>
   <si>
     <t>Status Indicators</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>状態表示</t>
@@ -1302,88 +664,88 @@
     <rPh sb="2" eb="4">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Color Coding</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>カラーコード</t>
   </si>
   <si>
     <t>Audible Signals</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可聴信号</t>
   </si>
   <si>
     <t>ICT With Two-Way Voice Communication</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>双方向音声通話機能付きICT</t>
   </si>
   <si>
     <t xml:space="preserve"> Volume Gain</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ボリュームゲイン</t>
   </si>
   <si>
     <t>Interference Reduction and Magnetic Coupling (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>妨害波低減と磁気結合（およびその下位規定）</t>
   </si>
   <si>
     <t>Digitally Encoded Speech</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>デジタル符号化音声</t>
   </si>
   <si>
     <t xml:space="preserve"> Real-Time Text Functionality (Reserved)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> リアルタイムテキスト機能(予約)</t>
   </si>
   <si>
     <t xml:space="preserve"> Caller ID</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 発信者番号通知</t>
   </si>
   <si>
     <t>Video Communication</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ビデオ通信</t>
   </si>
   <si>
     <t>Caption Processing Technologies</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプション処理技術</t>
   </si>
   <si>
     <t>General (includes sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（下位規定含む）</t>
   </si>
   <si>
     <t>Audio Description Processing Technology</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声説明処理技術</t>
@@ -1393,28 +755,28 @@
   </si>
   <si>
     <t>User Controls for Captions and Audio Description</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>字幕・音声説明のユーザー制御技術</t>
   </si>
   <si>
     <t>General (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（および下位規定）</t>
   </si>
   <si>
     <t>Interoperability With Assistive Technology</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>支援技術との相互運用性</t>
   </si>
   <si>
     <t>Accessibility Services (and sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティサービス（および下位規定）</t>
@@ -1424,164 +786,164 @@
   </si>
   <si>
     <t>Platform Accessibility Features</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プラットフォームアクセシビリティ機能</t>
   </si>
   <si>
     <t>A. Section 9.3.3</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Enable sequential entry of multiple (chorded) keystrokes</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>複数のキーストロークを連続して入力できる</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>B. Section 9.3.4</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of delay before key acceptance</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キー受理までの遅延時間の調整</t>
   </si>
   <si>
     <t>C. Section 9.3.5</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of same-key double-strike acceptance</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>同じキーの連打を受け入れるかどうかを調整できるようにした</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>D. Section 10.6.7</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Allow users to choose visual alternative for audio output</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力に代わる視覚的な選択肢をユーザーが選択可能</t>
   </si>
   <si>
     <t>E. Section 10.6.8</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Synchronize audio equivalents for visual events</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 視覚的イベントと音声を同期させる</t>
   </si>
   <si>
     <t>F. Section 10.6.9</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide speech output services</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力サービスの提供</t>
   </si>
   <si>
     <t>G. Section 10.7.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display any captions provided</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>提供されたキャプションの表示</t>
   </si>
   <si>
     <t>Applications</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アプリケーション</t>
   </si>
   <si>
     <t xml:space="preserve"> User Preferences</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ユーザー設定</t>
   </si>
   <si>
     <t>Alternative User Interfaces</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>代替ユーザーインターフェイス</t>
   </si>
   <si>
     <t>User Controls for Captions and Audio Description (includes sub-provisions)</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプションとオーディオディスクリプションのためのユーザーコントロール（下位規定を含む）</t>
   </si>
   <si>
     <t>Authoring Tools</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>オーサリングツール</t>
   </si>
   <si>
     <t xml:space="preserve"> Content Creation or Editing</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コンテンツの作成または編集</t>
   </si>
   <si>
     <t>504.2.1</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility in Format Conversion</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>フォーマット変換におけるアクセシビリティのための情報提供の保存</t>
   </si>
   <si>
     <t>504.2.2</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDF Export</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDFの書き出し</t>
   </si>
   <si>
     <t>Prompts</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プロンプト</t>
   </si>
   <si>
     <t>Templates</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>テンプレート</t>
@@ -1591,7 +953,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1613,13 +975,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1632,26 +987,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -1661,13 +1003,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1681,35 +1038,18 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="36"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="10.5"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -2046,184 +1386,184 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2247,16 +1587,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2593,230 +1933,230 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0A005FD-B30B-468F-A6FD-5A82171C81A4}">
-  <sheetPr codeName="Sheet239">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC2A4F94-71AA-48FD-B6E6-29764EA6BE21}">
+  <sheetPr codeName="Sheet276">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.58203125" style="3" customWidth="1"/>
-    <col min="5" max="7" width="9.08203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.58203125" style="3"/>
-    <col min="9" max="9" width="28.33203125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="8.58203125" style="3"/>
+    <col min="1" max="1" width="20.08203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.08203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.58203125" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9.08203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" style="2"/>
+    <col min="9" max="9" width="28.33203125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="11" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="19"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="19"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="19"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="19"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="2"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
       <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="27" t="s">
@@ -3160,28 +2500,28 @@
       <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="27" t="s">
@@ -3231,15 +2571,15 @@
       <c r="I44" s="42"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
@@ -3258,11 +2598,11 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="55"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="5"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="4"/>
       <c r="G47" s="56"/>
       <c r="H47" s="56"/>
       <c r="I47" s="57"/>
@@ -3407,9 +2747,9 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{50851CAB-D623-4AD8-84C4-10A5D8B13351}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{2B79D0F2-B59F-49CC-A749-FBD4AE531C96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3417,7 +2757,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA186AD-8532-4771-9D5D-8DE56EC95000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{913E9492-C2C3-4CB3-A82A-46BB79634A70}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3442,31 +2782,31 @@
         <v>56</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3474,36 +2814,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3511,10 +2851,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3532,14 +2872,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3555,15 +2895,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3578,15 +2918,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3601,17 +2941,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3624,10 +2964,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3635,7 +2975,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3647,10 +2987,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3659,7 +2999,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3670,10 +3010,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3683,10 +3023,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3695,10 +3035,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3708,10 +3048,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3720,10 +3060,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3741,17 +3081,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3766,10 +3106,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3787,10 +3127,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3805,17 +3145,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3828,17 +3168,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3851,20 +3191,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3876,20 +3216,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3901,17 +3241,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3927,10 +3267,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3938,7 +3278,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3947,23 +3287,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3972,23 +3312,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -4000,15 +3340,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -4023,15 +3363,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4046,27 +3386,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4075,10 +3415,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4096,29 +3436,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4127,10 +3467,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4148,17 +3488,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4173,10 +3513,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4194,30 +3534,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4225,10 +3565,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4246,31 +3586,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4279,10 +3619,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4300,15 +3640,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4323,14 +3663,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4346,10 +3686,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4359,10 +3699,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4371,27 +3711,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4400,10 +3740,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4413,10 +3753,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4425,14 +3765,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4448,10 +3788,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4461,10 +3801,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4473,10 +3813,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4486,10 +3826,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4498,10 +3838,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4519,10 +3859,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4540,10 +3880,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4561,14 +3901,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4584,10 +3924,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4605,15 +3945,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4628,10 +3968,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4649,20 +3989,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4674,10 +4014,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4695,29 +4035,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4726,10 +4066,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4747,10 +4087,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4758,7 +4098,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4770,10 +4110,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4781,7 +4121,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4793,10 +4133,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4804,7 +4144,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4816,10 +4156,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4837,24 +4177,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4866,17 +4206,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4889,20 +4229,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4914,10 +4254,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4935,14 +4275,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4958,10 +4298,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -4979,22 +4319,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -5006,10 +4346,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -5027,31 +4367,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5060,10 +4400,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5081,29 +4421,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5112,14 +4452,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5127,10 +4467,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5139,43 +4479,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5185,22 +4525,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5210,22 +4550,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5235,32 +4575,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5269,23 +4609,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5294,26 +4634,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5321,23 +4661,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5349,31 +4689,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5382,10 +4722,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5403,15 +4743,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5426,14 +4766,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5441,10 +4781,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5453,22 +4793,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5480,24 +4820,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5509,10 +4849,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5530,24 +4870,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5556,25 +4896,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5583,20 +4923,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5611,24 +4951,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5640,24 +4980,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>
@@ -5831,7 +5171,7 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
+++ b/file/Insights_Win32_Web_Android_iOS_VPATJ07060.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E697085D-D786-4DDF-8914-7D6ADFCD3354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EC3A916-F1EF-4B93-8E5B-F1FC4C4603C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{3E47D973-0004-4748-B330-617A673FFFBE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{976D6B51-517A-4725-873C-B83031035B69}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2024年5月14日</t>
+    <t>作成日：2024年10月8日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1933,8 +1933,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC2A4F94-71AA-48FD-B6E6-29764EA6BE21}">
-  <sheetPr codeName="Sheet276">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B20127F-193E-46E9-AE4B-1E0EE7AA6296}">
+  <sheetPr codeName="Sheet264">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2749,7 +2749,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{2B79D0F2-B59F-49CC-A749-FBD4AE531C96}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{456F63CD-2366-4FE4-9A69-27364A9D34E0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -2757,7 +2757,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{913E9492-C2C3-4CB3-A82A-46BB79634A70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C940B23-537A-4F30-A33C-6F724FF90074}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
